--- a/static/template_fins_de_bail.xlsx
+++ b/static/template_fins_de_bail.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,17 +30,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00888888"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,15 +71,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -468,7 +453,7 @@
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -502,113 +487,6 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Date entrée dans les lieux</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Identifiant unique (ex: ID Pipedrive)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Nom de la société</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Numéro SIREN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Adresse complète</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Code postal</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Date de début du bail (format JJ/MM/AAAA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>12345</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>ACME SAS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>10 rue de la Paix</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>75002</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>67890</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Tech Corp</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>25 avenue des Champs-Élysées</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>75008</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>01/06/2021</t>
         </is>
       </c>
     </row>

--- a/static/template_fins_de_bail.xlsx
+++ b/static/template_fins_de_bail.xlsx
@@ -441,16 +441,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Code postal</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -487,6 +487,76 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Date entrée dans les lieux</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12345</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Société Exemple SAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10 rue de la Paix</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>75002</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>01/03/2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67890</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dupont &amp; Fils SARL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>987654321</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5 avenue Victor Hugo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>69001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15/06/2018</t>
         </is>
       </c>
     </row>
